--- a/data/ams_weekly_data/Nexlev/ads_report_week35.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week35.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1530,10 +1530,10 @@
         <v>889</v>
       </c>
       <c r="G39" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1947,13 +1947,13 @@
         <v>1082</v>
       </c>
       <c r="F54" t="n">
-        <v>139363</v>
+        <v>139362</v>
       </c>
       <c r="G54" t="n">
-        <v>57174.58</v>
+        <v>62256.79</v>
       </c>
       <c r="H54" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55">
@@ -2118,10 +2118,10 @@
         <v>42013</v>
       </c>
       <c r="G60" t="n">
-        <v>14950.85</v>
+        <v>16814.41</v>
       </c>
       <c r="H60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -2426,10 +2426,10 @@
         <v>29870</v>
       </c>
       <c r="G71" t="n">
-        <v>20335.6</v>
+        <v>25419.5</v>
       </c>
       <c r="H71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -2734,10 +2734,10 @@
         <v>25326</v>
       </c>
       <c r="G82" t="n">
-        <v>3388.13</v>
+        <v>5082.2</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -4937,13 +4937,13 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>406.37</v>
+        <v>403.5</v>
       </c>
       <c r="E161" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F161" t="n">
-        <v>23276</v>
+        <v>23271</v>
       </c>
       <c r="G161" t="n">
         <v>6775.4</v>
@@ -5111,7 +5111,7 @@
         <v>16</v>
       </c>
       <c r="F167" t="n">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="G167" t="n">
         <v>1355.08</v>
@@ -6175,7 +6175,7 @@
         <v>2</v>
       </c>
       <c r="F205" t="n">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>30</v>
       </c>
       <c r="F213" t="n">
-        <v>5019</v>
+        <v>5018</v>
       </c>
       <c r="G213" t="n">
         <v>1439.83</v>
@@ -9821,7 +9821,7 @@
         <v>5590.68</v>
       </c>
       <c r="H335" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="336">
@@ -9874,10 +9874,10 @@
         <v>79068</v>
       </c>
       <c r="G337" t="n">
-        <v>5590.68</v>
+        <v>7454.24</v>
       </c>
       <c r="H337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="338">
@@ -10627,7 +10627,7 @@
         <v>88</v>
       </c>
       <c r="F364" t="n">
-        <v>9345</v>
+        <v>9344</v>
       </c>
       <c r="G364" t="n">
         <v>7186.440000000001</v>
@@ -10655,7 +10655,7 @@
         <v>931</v>
       </c>
       <c r="F365" t="n">
-        <v>58099</v>
+        <v>58096</v>
       </c>
       <c r="G365" t="n">
         <v>12703.4</v>
@@ -12047,7 +12047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12209,19 +12209,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7583</v>
+        <v>4772</v>
       </c>
       <c r="E5" t="n">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="F5" t="n">
-        <v>3299.74</v>
+        <v>2076.391617209016</v>
       </c>
       <c r="G5" t="n">
-        <v>14993.23</v>
+        <v>9434.627299995376</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -12233,28 +12233,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8576</v>
+        <v>2811</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="F6" t="n">
-        <v>1082.43</v>
+        <v>1223.348382790983</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>5558.602700004623</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -12266,28 +12266,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8133</v>
+        <v>8576</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>923.02</v>
+        <v>1082.43</v>
       </c>
       <c r="G7" t="n">
-        <v>2824.013333333333</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -12304,20 +12304,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8133</v>
+        <v>9757</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
-        <v>923.02</v>
+        <v>1107.403051496452</v>
       </c>
       <c r="G8" t="n">
-        <v>2824.013333333333</v>
+        <v>3388.14</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -12337,20 +12337,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8133</v>
+        <v>14641</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="F9" t="n">
-        <v>923.02</v>
+        <v>1661.656948503548</v>
       </c>
       <c r="G9" t="n">
-        <v>2824.013333333333</v>
+        <v>5083.9</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -12473,19 +12473,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14903</v>
+        <v>27322</v>
       </c>
       <c r="E13" t="n">
-        <v>875</v>
+        <v>1604</v>
       </c>
       <c r="F13" t="n">
-        <v>7035.993333333333</v>
+        <v>12899.08968311958</v>
       </c>
       <c r="G13" t="n">
-        <v>76323.02333333333</v>
+        <v>148626.0334378431</v>
       </c>
       <c r="H13" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -12506,19 +12506,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14903</v>
+        <v>7935</v>
       </c>
       <c r="E14" t="n">
-        <v>875</v>
+        <v>466</v>
       </c>
       <c r="F14" t="n">
-        <v>7035.993333333333</v>
+        <v>3746.11234507105</v>
       </c>
       <c r="G14" t="n">
-        <v>76323.02333333333</v>
+        <v>43163.49698607528</v>
       </c>
       <c r="H14" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -12539,19 +12539,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14903</v>
+        <v>9321</v>
       </c>
       <c r="E15" t="n">
-        <v>875</v>
+        <v>547</v>
       </c>
       <c r="F15" t="n">
-        <v>7035.993333333333</v>
+        <v>4400.43610140383</v>
       </c>
       <c r="G15" t="n">
-        <v>76323.02333333333</v>
+        <v>50702.75338919623</v>
       </c>
       <c r="H15" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -12563,28 +12563,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_KT_BM</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12434</v>
+        <v>132</v>
       </c>
       <c r="E16" t="n">
-        <v>366</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>2918.21</v>
+        <v>62.34187040554225</v>
       </c>
       <c r="G16" t="n">
-        <v>15248.32</v>
+        <v>718.316186885442</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_KT_BM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12605,19 +12605,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23440</v>
+        <v>8288</v>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>244</v>
       </c>
       <c r="F17" t="n">
-        <v>5217.18</v>
+        <v>1945.257712862794</v>
       </c>
       <c r="G17" t="n">
-        <v>36423.75999999999</v>
+        <v>12422.92965737865</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -12629,25 +12629,25 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_KT_BM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2959</v>
+        <v>4146</v>
       </c>
       <c r="E18" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F18" t="n">
-        <v>1349.32</v>
+        <v>972.952287137206</v>
       </c>
       <c r="G18" t="n">
-        <v>7031.360000000001</v>
+        <v>6213.53034262135</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
@@ -12662,28 +12662,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_PT</t>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9418</v>
+        <v>18750</v>
       </c>
       <c r="E19" t="n">
-        <v>197</v>
+        <v>510</v>
       </c>
       <c r="F19" t="n">
-        <v>1934.66</v>
+        <v>4173.71514029523</v>
       </c>
       <c r="G19" t="n">
-        <v>2880.51</v>
+        <v>29138.8065158725</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -12695,25 +12695,25 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_KT_Phrase</t>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>791</v>
+        <v>4688</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="F20" t="n">
-        <v>103.78</v>
+        <v>1043.464859704771</v>
       </c>
       <c r="G20" t="n">
-        <v>4574.58</v>
+        <v>7284.953484127484</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
@@ -12728,28 +12728,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_PT</t>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6578</v>
+        <v>1069</v>
       </c>
       <c r="E21" t="n">
-        <v>139</v>
+        <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>1616.78</v>
+        <v>487.5572204523733</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2540.68</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -12761,28 +12761,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1430</v>
+        <v>1890</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
-        <v>556.51</v>
+        <v>861.7627795476266</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4490.68</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -12794,28 +12794,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_PT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>231</v>
+        <v>9418</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>197</v>
       </c>
       <c r="F23" t="n">
-        <v>67.91</v>
+        <v>1934.66</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -12827,28 +12827,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - B0F43P6D23 - Phrase</t>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_KT_Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>335</v>
+        <v>498</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
-        <v>132.95</v>
+        <v>65.34792872788323</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -12860,28 +12860,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - SB - BM(2)</t>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_KT_Phrase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DKJZDY72</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>49.46</v>
+        <v>38.43207127211678</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -12893,28 +12893,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - SB - BM(3)</t>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_PT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>221</v>
+        <v>6578</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="F26" t="n">
-        <v>145.95</v>
+        <v>1616.78</v>
       </c>
       <c r="G26" t="n">
-        <v>3050</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - SB - Exact</t>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12935,19 +12935,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>344</v>
+        <v>1430</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="F27" t="n">
-        <v>176.9</v>
+        <v>556.51</v>
       </c>
       <c r="G27" t="n">
-        <v>2964.4</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - SB - Phrase</t>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>511</v>
+        <v>231</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>96.37</v>
+        <v>67.91</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -12992,30 +12992,195 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Nexlex - Steam Cleaner - B0F43P6D23 - Phrase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>335</v>
+      </c>
+      <c r="E29" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" t="n">
+        <v>132.95</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - BM(2)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>266</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - BM(3)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>221</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>145.95</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3050</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - Exact</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>344</v>
+      </c>
+      <c r="E32" t="n">
+        <v>11</v>
+      </c>
+      <c r="F32" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2964.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - Phrase</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>511</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>96.37</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Nexlex - Steame Cleaner - SB - Phrase</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>B0F43P6D23</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D34" t="n">
         <v>741</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E34" t="n">
         <v>8</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F34" t="n">
         <v>86.79000000000001</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>
